--- a/histograms/histogram_avg_f_valence_electrons.xlsx
+++ b/histograms/histogram_avg_f_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.125</v>
       </c>
       <c r="B2" t="n">
-        <v>20730</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.375</v>
       </c>
       <c r="B3" t="n">
-        <v>1045</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.625</v>
       </c>
       <c r="B4" t="n">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.875</v>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -485,7 +485,7 @@
         <v>1.375</v>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>1.625</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>1.875</v>
       </c>
       <c r="B9" t="n">
-        <v>221</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>2.125</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>2.375</v>
       </c>
       <c r="B11" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>2.625</v>
       </c>
       <c r="B12" t="n">
-        <v>835</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>2.875</v>
       </c>
       <c r="B13" t="n">
-        <v>996</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>3.125</v>
       </c>
       <c r="B14" t="n">
-        <v>1068</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>4.125</v>
       </c>
       <c r="B18" t="n">
-        <v>197</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>4.375</v>
       </c>
       <c r="B19" t="n">
-        <v>259</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -597,7 +597,7 @@
         <v>4.875</v>
       </c>
       <c r="B21" t="n">
-        <v>224</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
